--- a/sessions/04_phonology/att/wayground-minimal-pairs.xlsx
+++ b/sessions/04_phonology/att/wayground-minimal-pairs.xlsx
@@ -806,7 +806,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Are 'cod' and 'cord' minimal pairs?</t>
+          <t>Are 'cod' and 'cord' minimal pairs in BrE?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
